--- a/content/content.xlsx
+++ b/content/content.xlsx
@@ -13,13 +13,14 @@
     <sheet sheetId="7" name="members" state="visible" r:id="rId10"/>
     <sheet sheetId="8" name="balance" state="visible" r:id="rId11"/>
     <sheet sheetId="9" name="characters" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="attributes" state="visible" r:id="rId13"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="348">
   <si>
     <t>id</t>
   </si>
@@ -976,6 +977,93 @@
   </si>
   <si>
     <t>本来只是陪朋友来的，结果被留下了。</t>
+  </si>
+  <si>
+    <t>属性分类</t>
+  </si>
+  <si>
+    <t>属性名称</t>
+  </si>
+  <si>
+    <t>属性字段名</t>
+  </si>
+  <si>
+    <t>是否隐藏</t>
+  </si>
+  <si>
+    <t>关联属性</t>
+  </si>
+  <si>
+    <t>显性属性</t>
+  </si>
+  <si>
+    <t>演唱</t>
+  </si>
+  <si>
+    <t>FALSE</t>
+  </si>
+  <si>
+    <t>舞蹈</t>
+  </si>
+  <si>
+    <t>演技</t>
+  </si>
+  <si>
+    <t>口才</t>
+  </si>
+  <si>
+    <t>隐藏属性</t>
+  </si>
+  <si>
+    <t>自我</t>
+  </si>
+  <si>
+    <t>他人</t>
+  </si>
+  <si>
+    <t>适配</t>
+  </si>
+  <si>
+    <t>状态</t>
+  </si>
+  <si>
+    <t>体力</t>
+  </si>
+  <si>
+    <t>粉丝属性</t>
+  </si>
+  <si>
+    <t>舞台粉</t>
+  </si>
+  <si>
+    <t>stage</t>
+  </si>
+  <si>
+    <t>嘎起粉</t>
+  </si>
+  <si>
+    <t>gachi</t>
+  </si>
+  <si>
+    <t>音乐粉</t>
+  </si>
+  <si>
+    <t>music</t>
+  </si>
+  <si>
+    <t>现场粉</t>
+  </si>
+  <si>
+    <t>live</t>
+  </si>
+  <si>
+    <t>养成粉</t>
+  </si>
+  <si>
+    <t>实力粉</t>
+  </si>
+  <si>
+    <t>power</t>
   </si>
 </sst>
 </file>
@@ -1604,6 +1692,277 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="17" customWidth="1"/>
+    <col min="4" max="5" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>324</v>
+      </c>
+      <c r="B2" t="s">
+        <v>325</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>326</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>324</v>
+      </c>
+      <c r="B3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>326</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>324</v>
+      </c>
+      <c r="B4" t="s">
+        <v>328</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" t="s">
+        <v>326</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>324</v>
+      </c>
+      <c r="B5" t="s">
+        <v>329</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" t="s">
+        <v>326</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>330</v>
+      </c>
+      <c r="B6" t="s">
+        <v>331</v>
+      </c>
+      <c r="C6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>330</v>
+      </c>
+      <c r="B7" t="s">
+        <v>332</v>
+      </c>
+      <c r="C7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>330</v>
+      </c>
+      <c r="B8" t="s">
+        <v>333</v>
+      </c>
+      <c r="C8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D8" t="s">
+        <v>66</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>334</v>
+      </c>
+      <c r="B9" t="s">
+        <v>335</v>
+      </c>
+      <c r="C9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" t="s">
+        <v>326</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>336</v>
+      </c>
+      <c r="B10" t="s">
+        <v>337</v>
+      </c>
+      <c r="C10" t="s">
+        <v>338</v>
+      </c>
+      <c r="D10" t="s">
+        <v>326</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>336</v>
+      </c>
+      <c r="B11" t="s">
+        <v>339</v>
+      </c>
+      <c r="C11" t="s">
+        <v>340</v>
+      </c>
+      <c r="D11" t="s">
+        <v>326</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>336</v>
+      </c>
+      <c r="B12" t="s">
+        <v>341</v>
+      </c>
+      <c r="C12" t="s">
+        <v>342</v>
+      </c>
+      <c r="D12" t="s">
+        <v>326</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>336</v>
+      </c>
+      <c r="B13" t="s">
+        <v>343</v>
+      </c>
+      <c r="C13" t="s">
+        <v>344</v>
+      </c>
+      <c r="D13" t="s">
+        <v>326</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>336</v>
+      </c>
+      <c r="B14" t="s">
+        <v>345</v>
+      </c>
+      <c r="C14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" t="s">
+        <v>326</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>336</v>
+      </c>
+      <c r="B15" t="s">
+        <v>346</v>
+      </c>
+      <c r="C15" t="s">
+        <v>347</v>
+      </c>
+      <c r="D15" t="s">
+        <v>326</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E13"/>
